--- a/vendor_application_form_templates/042_cross_marketplace_listing_application--vendor_application_form_templates.xlsx
+++ b/vendor_application_form_templates/042_cross_marketplace_listing_application--vendor_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Shipping Cost</t>
+          <t>Shipping Cost Value</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shipping Weight</t>
+          <t>Shipping Weight Value</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>shipping_weight_unit</t>
+          <t>shipping_weight_unit_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shipping Weight Unit</t>
+          <t>Shipping Weight Unit 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shipping Price</t>
+          <t>Shipping Price Value</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'category1',_'label':_'category_1'}</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'category1', 'label': 'Category 1'}</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'category2',_'label':_'category_2'}</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'category2', 'label': 'Category 2'}</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'category3',_'label':_'category_3'}</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'category3', 'label': 'Category 3'}</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'image1',_'label':_'image_1'}</t>
+          <t>image_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'image1', 'label': 'Image 1'}</t>
+          <t>Image 1</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'image2',_'label':_'image_2'}</t>
+          <t>image_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'image2', 'label': 'Image 2'}</t>
+          <t>Image 2</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'image3',_'label':_'image_3'}</t>
+          <t>image_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'image3', 'label': 'Image 3'}</t>
+          <t>Image 3</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>shipping_weight_unit_choices</t>
+          <t>shipping_weight_unit_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>shipping_weight_unit_choices</t>
+          <t>shipping_weight_unit_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
